--- a/Gstsaralprotesting/src/test/java/pro/saral/testData/LoginData.xlsx
+++ b/Gstsaralprotesting/src/test/java/pro/saral/testData/LoginData.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujatha\Desktop\selenium\Gstsaralprotesting\src\test\java\pro\saral\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sujatha\git\Gstsaralprotesting\Gstsaralprotesting\src\test\java\pro\saral\testData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860FAD90-8C8D-4267-83B3-2CCA4768061D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F833416A-D32C-4D5C-81BA-CC15FC2CE367}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,9 +58,6 @@
     <t>darshan</t>
   </si>
   <si>
-    <t>Saral_Pro</t>
-  </si>
-  <si>
     <t>Rajajinagar</t>
   </si>
   <si>
@@ -239,6 +236,9 @@
   </si>
   <si>
     <t>29AAACC1206D2ZB</t>
+  </si>
+  <si>
+    <t>Saral_Pro_D</t>
   </si>
 </sst>
 </file>
@@ -707,51 +707,51 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>19</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+      <c r="H1" t="s">
         <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
-        <v>12</v>
-      </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E2">
         <v>580061</v>
       </c>
       <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" t="s">
         <v>13</v>
-      </c>
-      <c r="G2" t="s">
-        <v>14</v>
       </c>
       <c r="H2">
         <v>8976582536</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>25</v>
       </c>
       <c r="H3">
         <v>7477664645</v>
@@ -770,17 +770,17 @@
     </row>
     <row r="4" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>68</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>69</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="5">
         <v>560076</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="H4" s="5">
         <v>7632467562</v>
@@ -791,43 +791,43 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="C6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="I6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="J6" s="5" t="s">
         <v>45</v>
-      </c>
-      <c r="J6" s="5" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B7" s="5"/>
       <c r="C7" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5"/>
@@ -835,7 +835,7 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J7" s="5">
         <v>8736458356</v>
@@ -843,31 +843,31 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="F8" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>56</v>
       </c>
       <c r="J8" s="5">
         <v>8757656565</v>
@@ -875,26 +875,26 @@
     </row>
     <row r="9" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="C9" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C9" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D9" s="5" t="s">
+      <c r="E9" s="5" t="s">
         <v>65</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>66</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" s="7"/>
       <c r="J9" s="5">
@@ -908,40 +908,40 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="D11" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="G11" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="5" t="s">
+      <c r="I11" s="5" t="s">
         <v>33</v>
-      </c>
-      <c r="I11" s="5" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B12" s="6"/>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" s="5"/>
       <c r="E12" s="5"/>
@@ -952,28 +952,28 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="5" t="s">
         <v>39</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>40</v>
       </c>
       <c r="I13" s="5">
         <v>8393648292</v>
@@ -981,22 +981,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="D14" t="s">
         <v>59</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>61</v>
-      </c>
       <c r="G14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I14" s="5">
         <v>8393688292</v>
